--- a/database/seeders/data/06_CASILLEROS.xlsx
+++ b/database/seeders/data/06_CASILLEROS.xlsx
@@ -2,10 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CASILLEROS" sheetId="1" r:id="R5ed001e4d425405b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASIGNACIONES VIGENTES" sheetId="2" r:id="R522cd2bab1f54525"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BAJAS DE ASIGNACIONES" sheetId="3" r:id="R7f5bf0f030834540"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISTORIAL DE ASIGNACIONES" sheetId="4" r:id="Re20bb5dc74334b19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CASILLEROS" sheetId="1" r:id="Rd764728385e04a0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASIGNACIONES VIGENTES" sheetId="2" r:id="Rd4932b86c72a4207"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BAJAS DE ASIGNACIONES" sheetId="3" r:id="Rd523c065e0644f8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISTORIAL DE ASIGNACIONES" sheetId="4" r:id="R07fa38ce53524e1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="5" r:id="Rdb3d2b83f2024f3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EJEMPLOS" sheetId="6" r:id="R46ed83d676bc4196"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +18,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:numFmts count="3">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="201" formatCode="&quot;$&quot;#,##0.00"/>
+    <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd hh:mm"/>
+  </x:numFmts>
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -32,8 +39,47 @@
       <x:color rgb="FF222222"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFC0392B"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF2980B9"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1E8449"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="18">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -45,8 +91,83 @@
         <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC0392B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2980B9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1A252F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFADBD8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD6EAF8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD5F5E3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEBF5FB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1A252F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC0392B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2980B9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEBF5FB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1A252F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC0392B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2980B9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEBF5FB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -62,11 +183,25 @@
         <x:color rgb="FFFFFFFF"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="105">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -83,6 +218,204 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -296,16 +629,16 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>NÚMERO DEL CASILLERO</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="12" t="str">
         <x:v>CATEGORÍA</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="10" t="str">
         <x:v>ESTATUS</x:v>
       </x:c>
     </x:row>
@@ -1531,43 +1864,43 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>NÚMERO DEL CASILLERO</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="10" t="str">
         <x:v>NÚMERO DE SOCIO</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>NOMBRE</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="12" t="str">
         <x:v>APELLIDO PATERNO</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="12" t="str">
         <x:v>APELLIDO MATERNO</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="10" t="str">
         <x:v>NÚMERO DE MEMBRESÍA</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="10" t="str">
         <x:v>FECHA DE INICIO</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="I1" s="12" t="str">
         <x:v>FECHA DE TÉRMINO</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="J1" s="12" t="str">
         <x:v>AÑO DE LA ASIGNACIÓN</x:v>
       </x:c>
-      <x:c r="K1" s="6" t="str">
+      <x:c r="K1" s="12" t="str">
         <x:v>IMPORTE PAGADO</x:v>
       </x:c>
-      <x:c r="L1" s="6" t="str">
+      <x:c r="L1" s="10" t="str">
         <x:v>FOLIO O REFERENCIA DEL CARGO DE CASILLERO</x:v>
       </x:c>
-      <x:c r="M1" s="6" t="str">
+      <x:c r="M1" s="12" t="str">
         <x:v>NOMBRE O RUTA DEL ARCHIVO DE SOPORTE</x:v>
       </x:c>
     </x:row>
@@ -4586,49 +4919,49 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>NÚMERO DEL CASILLERO</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="10" t="str">
         <x:v>NÚMERO DE SOCIO</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>NOMBRE</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="12" t="str">
         <x:v>APELLIDO PATERNO</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="12" t="str">
         <x:v>APELLIDO MATERNO</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="10" t="str">
         <x:v>NÚMERO DE MEMBRESÍA</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="10" t="str">
         <x:v>FECHA DE INICIO</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="I1" s="12" t="str">
         <x:v>FECHA DE TÉRMINO</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="J1" s="12" t="str">
         <x:v>AÑO DE LA ASIGNACIÓN</x:v>
       </x:c>
-      <x:c r="K1" s="6" t="str">
+      <x:c r="K1" s="12" t="str">
         <x:v>IMPORTE PAGADO</x:v>
       </x:c>
-      <x:c r="L1" s="6" t="str">
+      <x:c r="L1" s="12" t="str">
         <x:v>FECHA DE BAJA</x:v>
       </x:c>
-      <x:c r="M1" s="6" t="str">
+      <x:c r="M1" s="12" t="str">
         <x:v>MOTIVO DE BAJA</x:v>
       </x:c>
-      <x:c r="N1" s="6" t="str">
+      <x:c r="N1" s="10" t="str">
         <x:v>FOLIO O REFERENCIA DEL CARGO DE CASILLERO</x:v>
       </x:c>
-      <x:c r="O1" s="6" t="str">
+      <x:c r="O1" s="12" t="str">
         <x:v>NOMBRE O RUTA DEL ARCHIVO DE SOPORTE</x:v>
       </x:c>
     </x:row>
@@ -8042,40 +8375,40 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>FOLIO O REFERENCIA DE LA ASIGNACIÓN ANTERIOR</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="10" t="str">
         <x:v>NÚMERO DE SOCIO</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>NOMBRE</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="12" t="str">
         <x:v>APELLIDO PATERNO</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="12" t="str">
         <x:v>APELLIDO MATERNO</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="10" t="str">
         <x:v>NÚMERO DE MEMBRESÍA</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="10" t="str">
         <x:v>NÚMERO DEL CASILLERO ANTERIOR</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="I1" s="10" t="str">
         <x:v>NÚMERO DEL CASILLERO NUEVO</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="J1" s="12" t="str">
         <x:v>FECHA Y HORA DEL CAMBIO</x:v>
       </x:c>
-      <x:c r="K1" s="6" t="str">
+      <x:c r="K1" s="12" t="str">
         <x:v>CORREO DE QUIEN REGISTRÓ EL CAMBIO</x:v>
       </x:c>
-      <x:c r="L1" s="6" t="str">
+      <x:c r="L1" s="12" t="str">
         <x:v>NOMBRE O RUTA DEL ARCHIVO DE SOPORTE</x:v>
       </x:c>
     </x:row>
@@ -10868,4 +11201,835 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF1A252F"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="76" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="4" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="34" t="str">
+        <x:v>INSTRUCCIONES DE CAPTURA</x:v>
+      </x:c>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="34"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="35"/>
+      <x:c r="B2" s="35"/>
+      <x:c r="C2" s="35"/>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="36" t="str">
+        <x:v>REGLAS GENERALES</x:v>
+      </x:c>
+      <x:c r="B3" s="36"/>
+      <x:c r="C3" s="36"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="37" t="str">
+        <x:v>ENCABEZADOS</x:v>
+      </x:c>
+      <x:c r="B4" s="38" t="str">
+        <x:v>No modificar los encabezados de las hojas de captura.</x:v>
+      </x:c>
+      <x:c r="C4" s="38"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="37" t="str">
+        <x:v>FECHAS</x:v>
+      </x:c>
+      <x:c r="B5" s="38" t="str">
+        <x:v>Usar formato AAAA-MM-DD. Para fecha y hora: AAAA-MM-DD HH:MM.</x:v>
+      </x:c>
+      <x:c r="C5" s="38"/>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="37" t="str">
+        <x:v>DATOS DESCONOCIDOS</x:v>
+      </x:c>
+      <x:c r="B6" s="38" t="str">
+        <x:v>Dejar la celda vacía cuando no se cuente con el dato.</x:v>
+      </x:c>
+      <x:c r="C6" s="38"/>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="37" t="str">
+        <x:v>REFERENCIAS</x:v>
+      </x:c>
+      <x:c r="B7" s="38" t="str">
+        <x:v>Repetir nombre, número de socio, membresía o folio; no usar IDs internos.</x:v>
+      </x:c>
+      <x:c r="C7" s="38"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="37" t="str">
+        <x:v>EJEMPLOS</x:v>
+      </x:c>
+      <x:c r="B8" s="38" t="str">
+        <x:v>La hoja EJEMPLOS es solo guía y no se debe importar como información real.</x:v>
+      </x:c>
+      <x:c r="C8" s="38"/>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="35"/>
+      <x:c r="B9" s="35"/>
+      <x:c r="C9" s="35"/>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="36" t="str">
+        <x:v>LEYENDA DE COLORES</x:v>
+      </x:c>
+      <x:c r="B10" s="36"/>
+      <x:c r="C10" s="36"/>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="39" t="str">
+        <x:v>ENCABEZADO ROJO</x:v>
+      </x:c>
+      <x:c r="B11" s="39" t="str">
+        <x:v>Campo básico para identificar o registrar el dato.</x:v>
+      </x:c>
+      <x:c r="C11" s="39"/>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="40" t="str">
+        <x:v>ENCABEZADO AZUL</x:v>
+      </x:c>
+      <x:c r="B12" s="40" t="str">
+        <x:v>Campo opcional; llenar cuando se cuente con la información.</x:v>
+      </x:c>
+      <x:c r="C12" s="40"/>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="41" t="str">
+        <x:v>ENCABEZADO VERDE</x:v>
+      </x:c>
+      <x:c r="B13" s="41" t="str">
+        <x:v>Catálogo de consulta o solo lectura. No modificar.</x:v>
+      </x:c>
+      <x:c r="C13" s="41"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:C1"/>
+    <x:mergeCell ref="A3:C3"/>
+    <x:mergeCell ref="A10:C10"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF1A252F"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="22" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="84" t="str">
+        <x:v>EJEMPLOS: CASILLEROS</x:v>
+      </x:c>
+      <x:c r="B1" s="84"/>
+      <x:c r="C1" s="84"/>
+      <x:c r="D1" s="84"/>
+    </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="90" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="B2" s="90" t="str">
+        <x:v>NÚMERO DEL CASILLERO</x:v>
+      </x:c>
+      <x:c r="C2" s="96" t="str">
+        <x:v>CATEGORÍA</x:v>
+      </x:c>
+      <x:c r="D2" s="90" t="str">
+        <x:v>ESTATUS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="101" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B3" s="101" t="str">
+        <x:v>A-101</x:v>
+      </x:c>
+      <x:c r="C3" s="101" t="str">
+        <x:v>DATOS DE EJEMPLO 1</x:v>
+      </x:c>
+      <x:c r="D3" s="101" t="str">
+        <x:v>ACTIVO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="101" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B4" s="101" t="str">
+        <x:v>B-204</x:v>
+      </x:c>
+      <x:c r="C4" s="101" t="str">
+        <x:v>DATOS DE EJEMPLO 2</x:v>
+      </x:c>
+      <x:c r="D4" s="101" t="str">
+        <x:v>PENDIENTE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="101" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B5" s="101" t="str">
+        <x:v>C-015</x:v>
+      </x:c>
+      <x:c r="C5" s="101" t="str">
+        <x:v>DATOS DE EJEMPLO 3</x:v>
+      </x:c>
+      <x:c r="D5" s="101" t="str">
+        <x:v>ACTIVO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6"/>
+      <x:c r="B6"/>
+      <x:c r="C6"/>
+      <x:c r="D6"/>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
+      <x:c r="M6"/>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
+      <x:c r="M7"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="84" t="str">
+        <x:v>EJEMPLOS: ASIGNACIONES VIGENTES</x:v>
+      </x:c>
+      <x:c r="B8" s="84"/>
+      <x:c r="C8" s="84"/>
+      <x:c r="D8" s="84"/>
+      <x:c r="E8" s="84"/>
+      <x:c r="F8" s="84"/>
+      <x:c r="G8" s="84"/>
+      <x:c r="H8" s="84"/>
+      <x:c r="I8" s="84"/>
+      <x:c r="J8" s="84"/>
+      <x:c r="K8" s="84"/>
+      <x:c r="L8" s="84"/>
+      <x:c r="M8" s="84"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="90" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="B9" s="90" t="str">
+        <x:v>NÚMERO DEL CASILLERO</x:v>
+      </x:c>
+      <x:c r="C9" s="90" t="str">
+        <x:v>NÚMERO DE SOCIO</x:v>
+      </x:c>
+      <x:c r="D9" s="96" t="str">
+        <x:v>NOMBRE</x:v>
+      </x:c>
+      <x:c r="E9" s="96" t="str">
+        <x:v>APELLIDO PATERNO</x:v>
+      </x:c>
+      <x:c r="F9" s="96" t="str">
+        <x:v>APELLIDO MATERNO</x:v>
+      </x:c>
+      <x:c r="G9" s="90" t="str">
+        <x:v>NÚMERO DE MEMBRESÍA</x:v>
+      </x:c>
+      <x:c r="H9" s="90" t="str">
+        <x:v>FECHA DE INICIO</x:v>
+      </x:c>
+      <x:c r="I9" s="96" t="str">
+        <x:v>FECHA DE TÉRMINO</x:v>
+      </x:c>
+      <x:c r="J9" s="96" t="str">
+        <x:v>AÑO DE LA ASIGNACIÓN</x:v>
+      </x:c>
+      <x:c r="K9" s="96" t="str">
+        <x:v>IMPORTE PAGADO</x:v>
+      </x:c>
+      <x:c r="L9" s="90" t="str">
+        <x:v>FOLIO O REFERENCIA DEL CARGO DE CASILLERO</x:v>
+      </x:c>
+      <x:c r="M9" s="96" t="str">
+        <x:v>NOMBRE O RUTA DEL ARCHIVO DE SOPORTE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="101" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B10" s="101" t="str">
+        <x:v>A-101</x:v>
+      </x:c>
+      <x:c r="C10" s="101" t="str">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="D10" s="101" t="str">
+        <x:v>Juan Carlos</x:v>
+      </x:c>
+      <x:c r="E10" s="101" t="str">
+        <x:v>Pérez</x:v>
+      </x:c>
+      <x:c r="F10" s="101" t="str">
+        <x:v>Hernández</x:v>
+      </x:c>
+      <x:c r="G10" s="101" t="str">
+        <x:v>M-1001</x:v>
+      </x:c>
+      <x:c r="H10" s="102" t="n">
+        <x:v>46037</x:v>
+      </x:c>
+      <x:c r="I10" s="102" t="n">
+        <x:v>46037</x:v>
+      </x:c>
+      <x:c r="J10" s="101" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="K10" s="103" t="n">
+        <x:v>2500</x:v>
+      </x:c>
+      <x:c r="L10" s="101" t="str">
+        <x:v>CARGO-2026-1001</x:v>
+      </x:c>
+      <x:c r="M10" s="101" t="str">
+        <x:v>documentos/socio-1001.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="101" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B11" s="101" t="str">
+        <x:v>B-204</x:v>
+      </x:c>
+      <x:c r="C11" s="101" t="str">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="D11" s="101" t="str">
+        <x:v>María Fernanda</x:v>
+      </x:c>
+      <x:c r="E11" s="101" t="str">
+        <x:v>López</x:v>
+      </x:c>
+      <x:c r="F11" s="101" t="str">
+        <x:v>García</x:v>
+      </x:c>
+      <x:c r="G11" s="101" t="str">
+        <x:v>M-1002</x:v>
+      </x:c>
+      <x:c r="H11" s="102" t="n">
+        <x:v>46044.291666666664</x:v>
+      </x:c>
+      <x:c r="I11" s="102" t="n">
+        <x:v>46044.291666666664</x:v>
+      </x:c>
+      <x:c r="J11" s="101" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="K11" s="103" t="n">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="L11" s="101" t="str">
+        <x:v>CARGO-2026-1002</x:v>
+      </x:c>
+      <x:c r="M11" s="101" t="str">
+        <x:v>documentos/socio-1002.pdf</x:v>
+      </x:c>
+      <x:c r="N11"/>
+      <x:c r="O11"/>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="101" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B12" s="101" t="str">
+        <x:v>C-015</x:v>
+      </x:c>
+      <x:c r="C12" s="101" t="str">
+        <x:v>1003</x:v>
+      </x:c>
+      <x:c r="D12" s="101" t="str">
+        <x:v>Roberto</x:v>
+      </x:c>
+      <x:c r="E12" s="101" t="str">
+        <x:v>Sánchez</x:v>
+      </x:c>
+      <x:c r="F12" s="101" t="str">
+        <x:v>Morales</x:v>
+      </x:c>
+      <x:c r="G12" s="101" t="str">
+        <x:v>M-1003</x:v>
+      </x:c>
+      <x:c r="H12" s="102" t="n">
+        <x:v>46051.333333333336</x:v>
+      </x:c>
+      <x:c r="I12" s="102" t="n">
+        <x:v>46051.333333333336</x:v>
+      </x:c>
+      <x:c r="J12" s="101" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="K12" s="103" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="L12" s="101" t="str">
+        <x:v>CARGO-2026-1003</x:v>
+      </x:c>
+      <x:c r="M12" s="101" t="str">
+        <x:v>documentos/socio-1003.pdf</x:v>
+      </x:c>
+      <x:c r="N12"/>
+      <x:c r="O12"/>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
+      <x:c r="M13"/>
+      <x:c r="N13"/>
+      <x:c r="O13"/>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="84" t="str">
+        <x:v>EJEMPLOS: BAJAS DE ASIGNACIONES</x:v>
+      </x:c>
+      <x:c r="B15" s="84"/>
+      <x:c r="C15" s="84"/>
+      <x:c r="D15" s="84"/>
+      <x:c r="E15" s="84"/>
+      <x:c r="F15" s="84"/>
+      <x:c r="G15" s="84"/>
+      <x:c r="H15" s="84"/>
+      <x:c r="I15" s="84"/>
+      <x:c r="J15" s="84"/>
+      <x:c r="K15" s="84"/>
+      <x:c r="L15" s="84"/>
+      <x:c r="M15" s="84"/>
+      <x:c r="N15" s="84"/>
+      <x:c r="O15" s="84"/>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="90" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="B16" s="90" t="str">
+        <x:v>NÚMERO DEL CASILLERO</x:v>
+      </x:c>
+      <x:c r="C16" s="90" t="str">
+        <x:v>NÚMERO DE SOCIO</x:v>
+      </x:c>
+      <x:c r="D16" s="96" t="str">
+        <x:v>NOMBRE</x:v>
+      </x:c>
+      <x:c r="E16" s="96" t="str">
+        <x:v>APELLIDO PATERNO</x:v>
+      </x:c>
+      <x:c r="F16" s="96" t="str">
+        <x:v>APELLIDO MATERNO</x:v>
+      </x:c>
+      <x:c r="G16" s="90" t="str">
+        <x:v>NÚMERO DE MEMBRESÍA</x:v>
+      </x:c>
+      <x:c r="H16" s="90" t="str">
+        <x:v>FECHA DE INICIO</x:v>
+      </x:c>
+      <x:c r="I16" s="96" t="str">
+        <x:v>FECHA DE TÉRMINO</x:v>
+      </x:c>
+      <x:c r="J16" s="96" t="str">
+        <x:v>AÑO DE LA ASIGNACIÓN</x:v>
+      </x:c>
+      <x:c r="K16" s="96" t="str">
+        <x:v>IMPORTE PAGADO</x:v>
+      </x:c>
+      <x:c r="L16" s="96" t="str">
+        <x:v>FECHA DE BAJA</x:v>
+      </x:c>
+      <x:c r="M16" s="96" t="str">
+        <x:v>MOTIVO DE BAJA</x:v>
+      </x:c>
+      <x:c r="N16" s="90" t="str">
+        <x:v>FOLIO O REFERENCIA DEL CARGO DE CASILLERO</x:v>
+      </x:c>
+      <x:c r="O16" s="96" t="str">
+        <x:v>NOMBRE O RUTA DEL ARCHIVO DE SOPORTE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="101" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B17" s="101" t="str">
+        <x:v>A-101</x:v>
+      </x:c>
+      <x:c r="C17" s="101" t="str">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="D17" s="101" t="str">
+        <x:v>Juan Carlos</x:v>
+      </x:c>
+      <x:c r="E17" s="101" t="str">
+        <x:v>Pérez</x:v>
+      </x:c>
+      <x:c r="F17" s="101" t="str">
+        <x:v>Hernández</x:v>
+      </x:c>
+      <x:c r="G17" s="101" t="str">
+        <x:v>M-1001</x:v>
+      </x:c>
+      <x:c r="H17" s="102" t="n">
+        <x:v>46037</x:v>
+      </x:c>
+      <x:c r="I17" s="102" t="n">
+        <x:v>46037</x:v>
+      </x:c>
+      <x:c r="J17" s="101" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="K17" s="103" t="n">
+        <x:v>2500</x:v>
+      </x:c>
+      <x:c r="L17" s="102" t="n">
+        <x:v>46037</x:v>
+      </x:c>
+      <x:c r="M17" s="101" t="str">
+        <x:v>Registro de ejemplo para el socio 1001.</x:v>
+      </x:c>
+      <x:c r="N17" s="101" t="str">
+        <x:v>CARGO-2026-1001</x:v>
+      </x:c>
+      <x:c r="O17" s="101" t="str">
+        <x:v>documentos/socio-1001.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="101" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B18" s="101" t="str">
+        <x:v>B-204</x:v>
+      </x:c>
+      <x:c r="C18" s="101" t="str">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="D18" s="101" t="str">
+        <x:v>María Fernanda</x:v>
+      </x:c>
+      <x:c r="E18" s="101" t="str">
+        <x:v>López</x:v>
+      </x:c>
+      <x:c r="F18" s="101" t="str">
+        <x:v>García</x:v>
+      </x:c>
+      <x:c r="G18" s="101" t="str">
+        <x:v>M-1002</x:v>
+      </x:c>
+      <x:c r="H18" s="102" t="n">
+        <x:v>46044.291666666664</x:v>
+      </x:c>
+      <x:c r="I18" s="102" t="n">
+        <x:v>46044.291666666664</x:v>
+      </x:c>
+      <x:c r="J18" s="101" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="K18" s="103" t="n">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="L18" s="102" t="n">
+        <x:v>46044.291666666664</x:v>
+      </x:c>
+      <x:c r="M18" s="101" t="str">
+        <x:v>Registro de ejemplo para el socio 1002.</x:v>
+      </x:c>
+      <x:c r="N18" s="101" t="str">
+        <x:v>CARGO-2026-1002</x:v>
+      </x:c>
+      <x:c r="O18" s="101" t="str">
+        <x:v>documentos/socio-1002.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="101" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B19" s="101" t="str">
+        <x:v>C-015</x:v>
+      </x:c>
+      <x:c r="C19" s="101" t="str">
+        <x:v>1003</x:v>
+      </x:c>
+      <x:c r="D19" s="101" t="str">
+        <x:v>Roberto</x:v>
+      </x:c>
+      <x:c r="E19" s="101" t="str">
+        <x:v>Sánchez</x:v>
+      </x:c>
+      <x:c r="F19" s="101" t="str">
+        <x:v>Morales</x:v>
+      </x:c>
+      <x:c r="G19" s="101" t="str">
+        <x:v>M-1003</x:v>
+      </x:c>
+      <x:c r="H19" s="102" t="n">
+        <x:v>46051.333333333336</x:v>
+      </x:c>
+      <x:c r="I19" s="102" t="n">
+        <x:v>46051.333333333336</x:v>
+      </x:c>
+      <x:c r="J19" s="101" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="K19" s="103" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="L19" s="102" t="n">
+        <x:v>46051.333333333336</x:v>
+      </x:c>
+      <x:c r="M19" s="101" t="str">
+        <x:v>Registro de ejemplo para el socio 1003.</x:v>
+      </x:c>
+      <x:c r="N19" s="101" t="str">
+        <x:v>CARGO-2026-1003</x:v>
+      </x:c>
+      <x:c r="O19" s="101" t="str">
+        <x:v>documentos/socio-1003.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="84" t="str">
+        <x:v>EJEMPLOS: HISTORIAL DE ASIGNACIONES</x:v>
+      </x:c>
+      <x:c r="B22" s="84"/>
+      <x:c r="C22" s="84"/>
+      <x:c r="D22" s="84"/>
+      <x:c r="E22" s="84"/>
+      <x:c r="F22" s="84"/>
+      <x:c r="G22" s="84"/>
+      <x:c r="H22" s="84"/>
+      <x:c r="I22" s="84"/>
+      <x:c r="J22" s="84"/>
+      <x:c r="K22" s="84"/>
+      <x:c r="L22" s="84"/>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="90" t="str">
+        <x:v>FOLIO O REFERENCIA DE LA ASIGNACIÓN ANTERIOR</x:v>
+      </x:c>
+      <x:c r="B23" s="90" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="C23" s="90" t="str">
+        <x:v>NÚMERO DE SOCIO</x:v>
+      </x:c>
+      <x:c r="D23" s="96" t="str">
+        <x:v>NOMBRE</x:v>
+      </x:c>
+      <x:c r="E23" s="96" t="str">
+        <x:v>APELLIDO PATERNO</x:v>
+      </x:c>
+      <x:c r="F23" s="96" t="str">
+        <x:v>APELLIDO MATERNO</x:v>
+      </x:c>
+      <x:c r="G23" s="90" t="str">
+        <x:v>NÚMERO DE MEMBRESÍA</x:v>
+      </x:c>
+      <x:c r="H23" s="90" t="str">
+        <x:v>NÚMERO DEL CASILLERO ANTERIOR</x:v>
+      </x:c>
+      <x:c r="I23" s="90" t="str">
+        <x:v>NÚMERO DEL CASILLERO NUEVO</x:v>
+      </x:c>
+      <x:c r="J23" s="96" t="str">
+        <x:v>FECHA Y HORA DEL CAMBIO</x:v>
+      </x:c>
+      <x:c r="K23" s="96" t="str">
+        <x:v>CORREO DE QUIEN REGISTRÓ EL CAMBIO</x:v>
+      </x:c>
+      <x:c r="L23" s="96" t="str">
+        <x:v>NOMBRE O RUTA DEL ARCHIVO DE SOPORTE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="101" t="str">
+        <x:v>ASI-2026-1001</x:v>
+      </x:c>
+      <x:c r="B24" s="101" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="C24" s="101" t="str">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="D24" s="101" t="str">
+        <x:v>Juan Carlos</x:v>
+      </x:c>
+      <x:c r="E24" s="101" t="str">
+        <x:v>Pérez</x:v>
+      </x:c>
+      <x:c r="F24" s="101" t="str">
+        <x:v>Hernández</x:v>
+      </x:c>
+      <x:c r="G24" s="101" t="str">
+        <x:v>M-1001</x:v>
+      </x:c>
+      <x:c r="H24" s="101" t="str">
+        <x:v>A-101</x:v>
+      </x:c>
+      <x:c r="I24" s="101" t="str">
+        <x:v>A-101</x:v>
+      </x:c>
+      <x:c r="J24" s="104" t="n">
+        <x:v>46037.625</x:v>
+      </x:c>
+      <x:c r="K24" s="101" t="str">
+        <x:v>juan.perez@example.com</x:v>
+      </x:c>
+      <x:c r="L24" s="101" t="str">
+        <x:v>documentos/socio-1001.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="101" t="str">
+        <x:v>ASI-2026-1002</x:v>
+      </x:c>
+      <x:c r="B25" s="101" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="C25" s="101" t="str">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="D25" s="101" t="str">
+        <x:v>María Fernanda</x:v>
+      </x:c>
+      <x:c r="E25" s="101" t="str">
+        <x:v>López</x:v>
+      </x:c>
+      <x:c r="F25" s="101" t="str">
+        <x:v>García</x:v>
+      </x:c>
+      <x:c r="G25" s="101" t="str">
+        <x:v>M-1002</x:v>
+      </x:c>
+      <x:c r="H25" s="101" t="str">
+        <x:v>B-204</x:v>
+      </x:c>
+      <x:c r="I25" s="101" t="str">
+        <x:v>B-204</x:v>
+      </x:c>
+      <x:c r="J25" s="104" t="n">
+        <x:v>46044.666666666664</x:v>
+      </x:c>
+      <x:c r="K25" s="101" t="str">
+        <x:v>maria.lopez@example.com</x:v>
+      </x:c>
+      <x:c r="L25" s="101" t="str">
+        <x:v>documentos/socio-1002.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="24" customHeight="1">
+      <x:c r="A26" s="101" t="str">
+        <x:v>ASI-2026-1003</x:v>
+      </x:c>
+      <x:c r="B26" s="101" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="C26" s="101" t="str">
+        <x:v>1003</x:v>
+      </x:c>
+      <x:c r="D26" s="101" t="str">
+        <x:v>Roberto</x:v>
+      </x:c>
+      <x:c r="E26" s="101" t="str">
+        <x:v>Sánchez</x:v>
+      </x:c>
+      <x:c r="F26" s="101" t="str">
+        <x:v>Morales</x:v>
+      </x:c>
+      <x:c r="G26" s="101" t="str">
+        <x:v>M-1003</x:v>
+      </x:c>
+      <x:c r="H26" s="101" t="str">
+        <x:v>C-015</x:v>
+      </x:c>
+      <x:c r="I26" s="101" t="str">
+        <x:v>C-015</x:v>
+      </x:c>
+      <x:c r="J26" s="104" t="n">
+        <x:v>46051.708333333336</x:v>
+      </x:c>
+      <x:c r="K26" s="101" t="str">
+        <x:v>roberto.sanchez@example.com</x:v>
+      </x:c>
+      <x:c r="L26" s="101" t="str">
+        <x:v>documentos/socio-1003.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A8:M8"/>
+    <x:mergeCell ref="A15:O15"/>
+    <x:mergeCell ref="A22:L22"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>